--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -94,24 +94,12 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -880,6 +868,12 @@
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5503</t>
   </si>
   <si>
@@ -1336,6 +1330,12 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4202</t>
   </si>
   <si>
@@ -2092,7 +2092,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:19</t>
+    <t xml:space="preserve">2026-09-09 20:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2732,7 +2732,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>80.03</v>
+        <v>79.9</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2764,7 +2764,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>79.9</v>
+        <v>78.76</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2796,7 +2796,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>79.74</v>
+        <v>78.54</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2807,10 +2807,10 @@
         <v>2021</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2828,7 +2828,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>78.76</v>
+        <v>76.35</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2839,10 +2839,10 @@
         <v>2021</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
@@ -2860,7 +2860,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>78.54</v>
+        <v>75.71</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2871,10 +2871,10 @@
         <v>2021</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
@@ -2892,7 +2892,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>76.35</v>
+        <v>75.49</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2903,10 +2903,10 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
@@ -2924,7 +2924,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>75.71</v>
+        <v>74.64</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2935,10 +2935,10 @@
         <v>2021</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2956,7 +2956,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>75.49</v>
+        <v>73.79</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -2967,10 +2967,10 @@
         <v>2021</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -2988,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>74.64</v>
+        <v>60.61</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -2999,28 +2999,28 @@
         <v>2021</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>73.79</v>
+        <v>85.41</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3031,28 +3031,28 @@
         <v>2021</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>60.61</v>
+        <v>84.83</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3066,25 +3066,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>85.41</v>
+        <v>81.89</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3098,7 +3098,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>52</v>
@@ -3107,16 +3107,16 @@
         <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>84.83</v>
+        <v>81.18</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3127,28 +3127,28 @@
         <v>2021</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>81.89</v>
+        <v>79.33</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3159,28 +3159,28 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>81.18</v>
+        <v>78.85</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3191,28 +3191,28 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>79.33</v>
+        <v>78.62</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3223,28 +3223,28 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>78.85</v>
+        <v>78.35</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3255,28 +3255,28 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>78.62</v>
+        <v>78.12</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3287,28 +3287,28 @@
         <v>2021</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>78.35</v>
+        <v>78.08</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3319,10 +3319,10 @@
         <v>2021</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3331,16 +3331,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>78.12</v>
+        <v>77.92</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3351,10 +3351,10 @@
         <v>2021</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3363,16 +3363,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>78.08</v>
+        <v>77.82</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3383,10 +3383,10 @@
         <v>2021</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3395,16 +3395,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>77.92</v>
+        <v>77.62</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3418,7 +3418,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3427,16 +3427,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>77.82</v>
+        <v>77.6</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3447,10 +3447,10 @@
         <v>2021</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3459,16 +3459,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>77.62</v>
+        <v>77.42</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3479,10 +3479,10 @@
         <v>2021</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3491,16 +3491,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>77.6</v>
+        <v>77.36</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3514,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3523,16 +3523,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>77.42</v>
+        <v>76.75</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3546,7 +3546,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3555,16 +3555,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>77.36</v>
+        <v>76.73</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3575,10 +3575,10 @@
         <v>2021</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3587,16 +3587,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>76.75</v>
+        <v>76.64</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3607,10 +3607,10 @@
         <v>2021</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3619,16 +3619,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>76.73</v>
+        <v>76.63</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3639,10 +3639,10 @@
         <v>2021</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3651,16 +3651,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>76.64</v>
+        <v>76.61</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3671,10 +3671,10 @@
         <v>2021</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3683,16 +3683,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>76.63</v>
+        <v>76.6</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3703,10 +3703,10 @@
         <v>2021</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3715,16 +3715,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>76.61</v>
+        <v>76.59</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3735,10 +3735,10 @@
         <v>2021</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3747,16 +3747,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>76.6</v>
+        <v>76.57</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3770,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3779,16 +3779,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>76.59</v>
+        <v>76.49</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3799,10 +3799,10 @@
         <v>2021</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3811,16 +3811,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>76.57</v>
+        <v>76.46</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3834,7 +3834,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3843,16 +3843,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>76.49</v>
+        <v>76.22</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3863,28 +3863,28 @@
         <v>2021</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>76.46</v>
+        <v>76.17</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3895,28 +3895,28 @@
         <v>2021</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>76.22</v>
+        <v>76.16</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3927,28 +3927,28 @@
         <v>2021</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>76.17</v>
+        <v>76.09</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3959,10 +3959,10 @@
         <v>2021</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -3971,16 +3971,16 @@
         <v>110</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>76.16</v>
+        <v>76.03</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -4003,16 +4003,16 @@
         <v>112</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>76.09</v>
+        <v>76.02</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4023,10 +4023,10 @@
         <v>2021</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -4035,16 +4035,16 @@
         <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>76.03</v>
+        <v>75.94</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4055,10 +4055,10 @@
         <v>2021</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4067,16 +4067,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>76.02</v>
+        <v>75.81</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4087,10 +4087,10 @@
         <v>2021</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4099,16 +4099,16 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>75.94</v>
+        <v>75.6</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4119,10 +4119,10 @@
         <v>2021</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4131,16 +4131,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>75.81</v>
+        <v>75.56</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4151,10 +4151,10 @@
         <v>2021</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4163,16 +4163,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>75.6</v>
+        <v>75.55</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4183,10 +4183,10 @@
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4195,16 +4195,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4215,10 +4215,10 @@
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4227,16 +4227,16 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>75.55</v>
+        <v>75.5</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4250,7 +4250,7 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4259,16 +4259,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>75.52</v>
+        <v>75.48</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4279,10 +4279,10 @@
         <v>2021</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4291,16 +4291,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>75.5</v>
+        <v>75.46</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4311,10 +4311,10 @@
         <v>2021</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4323,16 +4323,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>75.48</v>
+        <v>75.44</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4343,10 +4343,10 @@
         <v>2021</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4355,16 +4355,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>75.46</v>
+        <v>75.36</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4375,10 +4375,10 @@
         <v>2021</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4387,16 +4387,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>75.44</v>
+        <v>75.35</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4407,10 +4407,10 @@
         <v>2021</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4419,16 +4419,16 @@
         <v>138</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>75.36</v>
+        <v>75.33</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4439,10 +4439,10 @@
         <v>2021</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4451,16 +4451,16 @@
         <v>140</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>75.35</v>
+        <v>75.33</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4471,10 +4471,10 @@
         <v>2021</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4483,10 +4483,10 @@
         <v>142</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4503,10 +4503,10 @@
         <v>2021</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4515,10 +4515,10 @@
         <v>144</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4535,10 +4535,10 @@
         <v>2021</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4547,16 +4547,16 @@
         <v>146</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>75.33</v>
+        <v>75.3</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4570,7 +4570,7 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4579,16 +4579,16 @@
         <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>75.33</v>
+        <v>75.28</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4602,7 +4602,7 @@
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -4611,16 +4611,16 @@
         <v>150</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>75.3</v>
+        <v>75.17</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4631,10 +4631,10 @@
         <v>2021</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4643,16 +4643,16 @@
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>75.28</v>
+        <v>75.16</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4663,10 +4663,10 @@
         <v>2021</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4675,16 +4675,16 @@
         <v>154</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4695,10 +4695,10 @@
         <v>2021</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4707,16 +4707,16 @@
         <v>156</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>75.16</v>
+        <v>75.13</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4727,10 +4727,10 @@
         <v>2021</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4739,16 +4739,16 @@
         <v>158</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>75.14</v>
+        <v>75.1</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4759,10 +4759,10 @@
         <v>2021</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4771,16 +4771,16 @@
         <v>160</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75.13</v>
+        <v>75.08</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4791,10 +4791,10 @@
         <v>2021</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4803,16 +4803,16 @@
         <v>162</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>75.1</v>
+        <v>75.04</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4823,10 +4823,10 @@
         <v>2021</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4835,16 +4835,16 @@
         <v>164</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>75.08</v>
+        <v>74.99</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4858,7 +4858,7 @@
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4867,16 +4867,16 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>75.04</v>
+        <v>74.97</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4887,10 +4887,10 @@
         <v>2021</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4899,16 +4899,16 @@
         <v>168</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>74.99</v>
+        <v>74.82</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4919,10 +4919,10 @@
         <v>2021</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -4931,16 +4931,16 @@
         <v>170</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>74.97</v>
+        <v>74.8</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4951,10 +4951,10 @@
         <v>2021</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -4963,16 +4963,16 @@
         <v>172</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>74.82</v>
+        <v>74.73</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4983,10 +4983,10 @@
         <v>2021</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -4995,16 +4995,16 @@
         <v>174</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>74.8</v>
+        <v>74.68</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -5018,7 +5018,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5027,16 +5027,16 @@
         <v>176</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>74.73</v>
+        <v>74.63</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5047,10 +5047,10 @@
         <v>2021</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5059,16 +5059,16 @@
         <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>74.68</v>
+        <v>74.59</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5079,10 +5079,10 @@
         <v>2021</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5091,16 +5091,16 @@
         <v>180</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>74.63</v>
+        <v>74.55</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5111,10 +5111,10 @@
         <v>2021</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5123,16 +5123,16 @@
         <v>182</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>74.59</v>
+        <v>74.54</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5143,10 +5143,10 @@
         <v>2021</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5155,16 +5155,16 @@
         <v>184</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>74.55</v>
+        <v>74.53</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5187,16 +5187,16 @@
         <v>186</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>74.54</v>
+        <v>74.51</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>187</v>
@@ -5219,16 +5219,16 @@
         <v>188</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>74.53</v>
+        <v>74.42</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5242,7 +5242,7 @@
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5251,16 +5251,16 @@
         <v>190</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>74.51</v>
+        <v>74.38</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5271,10 +5271,10 @@
         <v>2021</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5283,16 +5283,16 @@
         <v>192</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>74.42</v>
+        <v>74.38</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5303,10 +5303,10 @@
         <v>2021</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5315,16 +5315,16 @@
         <v>194</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>74.38</v>
+        <v>74.35</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5335,10 +5335,10 @@
         <v>2021</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5347,16 +5347,16 @@
         <v>196</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>74.38</v>
+        <v>74.33</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5367,10 +5367,10 @@
         <v>2021</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5379,16 +5379,16 @@
         <v>198</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>74.35</v>
+        <v>74.3</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5399,10 +5399,10 @@
         <v>2021</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5411,16 +5411,16 @@
         <v>200</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>74.33</v>
+        <v>74.26</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5431,10 +5431,10 @@
         <v>2021</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5443,16 +5443,16 @@
         <v>202</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>74.3</v>
+        <v>74.24</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5463,10 +5463,10 @@
         <v>2021</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5475,16 +5475,16 @@
         <v>204</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>74.26</v>
+        <v>74.22</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5495,10 +5495,10 @@
         <v>2021</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5507,16 +5507,16 @@
         <v>206</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>74.24</v>
+        <v>74.21</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5527,10 +5527,10 @@
         <v>2021</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5539,16 +5539,16 @@
         <v>208</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>74.22</v>
+        <v>74.19</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5559,10 +5559,10 @@
         <v>2021</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5571,16 +5571,16 @@
         <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>74.21</v>
+        <v>74.18</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5594,7 +5594,7 @@
         <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>211</v>
@@ -5603,16 +5603,16 @@
         <v>212</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>74.19</v>
+        <v>74.11</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5623,10 +5623,10 @@
         <v>2021</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5635,16 +5635,16 @@
         <v>214</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>74.18</v>
+        <v>74.08</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5658,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5667,16 +5667,16 @@
         <v>216</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>74.11</v>
+        <v>73.98</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5687,10 +5687,10 @@
         <v>2021</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5699,16 +5699,16 @@
         <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>74.08</v>
+        <v>73.95</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5719,10 +5719,10 @@
         <v>2021</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5731,16 +5731,16 @@
         <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>73.98</v>
+        <v>73.93</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5751,10 +5751,10 @@
         <v>2021</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5763,16 +5763,16 @@
         <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>73.95</v>
+        <v>73.88</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5783,10 +5783,10 @@
         <v>2021</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5795,16 +5795,16 @@
         <v>224</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>73.93</v>
+        <v>73.87</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5815,10 +5815,10 @@
         <v>2021</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5827,16 +5827,16 @@
         <v>226</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>73.88</v>
+        <v>73.86</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5847,10 +5847,10 @@
         <v>2021</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5859,16 +5859,16 @@
         <v>228</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>73.87</v>
+        <v>73.79</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5879,10 +5879,10 @@
         <v>2021</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5891,16 +5891,16 @@
         <v>230</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>73.86</v>
+        <v>73.78</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5911,10 +5911,10 @@
         <v>2021</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5923,16 +5923,16 @@
         <v>232</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>73.79</v>
+        <v>73.77</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5943,10 +5943,10 @@
         <v>2021</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -5955,16 +5955,16 @@
         <v>234</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>73.78</v>
+        <v>73.72</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5975,10 +5975,10 @@
         <v>2021</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -5987,16 +5987,16 @@
         <v>236</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>73.77</v>
+        <v>73.71</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6007,10 +6007,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6019,16 +6019,16 @@
         <v>238</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>73.72</v>
+        <v>73.71</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6039,10 +6039,10 @@
         <v>2021</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6051,16 +6051,16 @@
         <v>240</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>73.71</v>
+        <v>73.65</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6074,7 +6074,7 @@
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6083,16 +6083,16 @@
         <v>242</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>73.71</v>
+        <v>73.58</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6103,10 +6103,10 @@
         <v>2021</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6115,16 +6115,16 @@
         <v>244</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>73.65</v>
+        <v>73.57</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6135,10 +6135,10 @@
         <v>2021</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>245</v>
@@ -6147,16 +6147,16 @@
         <v>246</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>73.58</v>
+        <v>73.53</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6167,10 +6167,10 @@
         <v>2021</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6179,16 +6179,16 @@
         <v>248</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>73.57</v>
+        <v>73.43</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6199,10 +6199,10 @@
         <v>2021</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>249</v>
@@ -6211,16 +6211,16 @@
         <v>250</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>73.53</v>
+        <v>73.43</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6231,10 +6231,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6243,16 +6243,16 @@
         <v>252</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>73.43</v>
+        <v>73.41</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6263,10 +6263,10 @@
         <v>2021</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6275,16 +6275,16 @@
         <v>254</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>73.43</v>
+        <v>73.41</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6295,10 +6295,10 @@
         <v>2021</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6307,16 +6307,16 @@
         <v>256</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>73.41</v>
+        <v>73.33</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6327,10 +6327,10 @@
         <v>2021</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6339,16 +6339,16 @@
         <v>258</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>73.41</v>
+        <v>73.3</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6359,10 +6359,10 @@
         <v>2021</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6371,16 +6371,16 @@
         <v>260</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>73.33</v>
+        <v>73.2</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6391,10 +6391,10 @@
         <v>2021</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6403,16 +6403,16 @@
         <v>262</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>73.3</v>
+        <v>73.19</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6423,10 +6423,10 @@
         <v>2021</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6435,16 +6435,16 @@
         <v>264</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6455,10 +6455,10 @@
         <v>2021</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6467,16 +6467,16 @@
         <v>266</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>73.19</v>
+        <v>73.06</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6487,10 +6487,10 @@
         <v>2021</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6499,16 +6499,16 @@
         <v>268</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>73.14</v>
+        <v>73.04</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6519,10 +6519,10 @@
         <v>2021</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6531,16 +6531,16 @@
         <v>270</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>73.06</v>
+        <v>73.03</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6554,7 +6554,7 @@
         <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6563,16 +6563,16 @@
         <v>272</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>73.04</v>
+        <v>72.93</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6583,10 +6583,10 @@
         <v>2021</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6595,16 +6595,16 @@
         <v>274</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>73.03</v>
+        <v>72.92</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6615,10 +6615,10 @@
         <v>2021</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6627,16 +6627,16 @@
         <v>276</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>72.93</v>
+        <v>72.89</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6647,10 +6647,10 @@
         <v>2021</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6659,16 +6659,16 @@
         <v>278</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>72.92</v>
+        <v>72.79</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6679,10 +6679,10 @@
         <v>2021</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6691,16 +6691,16 @@
         <v>280</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>72.89</v>
+        <v>72.78</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6711,10 +6711,10 @@
         <v>2021</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6723,16 +6723,16 @@
         <v>282</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>72.79</v>
+        <v>72.72</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6743,10 +6743,10 @@
         <v>2021</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6755,16 +6755,16 @@
         <v>284</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>72.78</v>
+        <v>72.7</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6778,7 +6778,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6787,16 +6787,16 @@
         <v>286</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>72.72</v>
+        <v>72.56</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6807,10 +6807,10 @@
         <v>2021</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6819,16 +6819,16 @@
         <v>288</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>72.56</v>
+        <v>72.55</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6842,7 +6842,7 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6851,16 +6851,16 @@
         <v>290</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>72.55</v>
+        <v>72.48</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6874,7 +6874,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>291</v>
@@ -6883,16 +6883,16 @@
         <v>292</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>72.48</v>
+        <v>72.45</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6906,7 +6906,7 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6915,16 +6915,16 @@
         <v>294</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>72.45</v>
+        <v>72.35</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6935,10 +6935,10 @@
         <v>2021</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -6947,16 +6947,16 @@
         <v>296</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>72.35</v>
+        <v>72.32</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6967,10 +6967,10 @@
         <v>2021</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -6979,16 +6979,16 @@
         <v>298</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>72.32</v>
+        <v>72.28</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -6999,10 +6999,10 @@
         <v>2021</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7011,16 +7011,16 @@
         <v>300</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>72.28</v>
+        <v>72.23</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7031,10 +7031,10 @@
         <v>2021</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7043,16 +7043,16 @@
         <v>302</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>72.23</v>
+        <v>72.22</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -7063,10 +7063,10 @@
         <v>2021</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7075,16 +7075,16 @@
         <v>304</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>72.22</v>
+        <v>72.19</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7095,10 +7095,10 @@
         <v>2021</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7107,16 +7107,16 @@
         <v>306</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>72.19</v>
+        <v>72.16</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7130,7 +7130,7 @@
         <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7139,16 +7139,16 @@
         <v>308</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>72.16</v>
+        <v>72.11</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -7162,7 +7162,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7171,16 +7171,16 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>72.11</v>
+        <v>72.07</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7191,10 +7191,10 @@
         <v>2021</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7203,16 +7203,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>72.07</v>
+        <v>72.05</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7223,10 +7223,10 @@
         <v>2021</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7235,16 +7235,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>72.05</v>
+        <v>72</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7255,10 +7255,10 @@
         <v>2021</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7267,16 +7267,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>72</v>
+        <v>71.96</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7290,7 +7290,7 @@
         <v>6</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7299,16 +7299,16 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>71.96</v>
+        <v>71.94</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7319,10 +7319,10 @@
         <v>2021</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7331,16 +7331,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>71.94</v>
+        <v>71.86</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7354,7 +7354,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7363,16 +7363,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>71.86</v>
+        <v>71.85</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7383,10 +7383,10 @@
         <v>2021</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7395,16 +7395,16 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>71.85</v>
+        <v>71.78</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7418,7 +7418,7 @@
         <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7427,16 +7427,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>71.78</v>
+        <v>71.76</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7450,7 +7450,7 @@
         <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7459,16 +7459,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>71.76</v>
+        <v>71.65</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7479,10 +7479,10 @@
         <v>2021</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7491,16 +7491,16 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>71.65</v>
+        <v>71.63</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7511,10 +7511,10 @@
         <v>2021</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7523,16 +7523,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>71.63</v>
+        <v>71.6</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7543,10 +7543,10 @@
         <v>2021</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7555,16 +7555,16 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>71.6</v>
+        <v>71.5</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7578,7 +7578,7 @@
         <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7587,16 +7587,16 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>71.5</v>
+        <v>71.35</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7607,10 +7607,10 @@
         <v>2021</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7619,16 +7619,16 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>71.35</v>
+        <v>71.14</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7639,10 +7639,10 @@
         <v>2021</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7651,16 +7651,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>71.14</v>
+        <v>71.02</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7671,10 +7671,10 @@
         <v>2021</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7683,16 +7683,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>71.02</v>
+        <v>70.78</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7703,10 +7703,10 @@
         <v>2021</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7715,16 +7715,16 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>70.78</v>
+        <v>70.7</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7738,7 +7738,7 @@
         <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7747,16 +7747,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>70.7</v>
+        <v>70.57</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7770,7 +7770,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7779,16 +7779,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>70.57</v>
+        <v>70.33</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7802,7 +7802,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7811,16 +7811,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>70.33</v>
+        <v>70.17</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7834,7 +7834,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7843,16 +7843,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>70.17</v>
+        <v>70.13</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7866,7 +7866,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7875,16 +7875,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>70.13</v>
+        <v>70.09</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7895,10 +7895,10 @@
         <v>2021</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7907,16 +7907,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>70.09</v>
+        <v>69.98</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7927,10 +7927,10 @@
         <v>2021</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7939,16 +7939,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>69.98</v>
+        <v>69.6</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7959,10 +7959,10 @@
         <v>2021</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -7971,16 +7971,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>69.6</v>
+        <v>68.57</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -7991,10 +7991,10 @@
         <v>2021</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8003,16 +8003,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>68.57</v>
+        <v>68.54</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8026,7 +8026,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8035,16 +8035,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>68.54</v>
+        <v>68.41</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -8058,7 +8058,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8067,16 +8067,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>68.41</v>
+        <v>68.27</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8087,10 +8087,10 @@
         <v>2021</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8099,16 +8099,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>68.27</v>
+        <v>68.24</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8119,10 +8119,10 @@
         <v>2021</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8131,16 +8131,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>68.24</v>
+        <v>68.21</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8151,10 +8151,10 @@
         <v>2021</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8163,16 +8163,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>68.21</v>
+        <v>68.09</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8183,10 +8183,10 @@
         <v>2021</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8195,16 +8195,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>68.09</v>
+        <v>67.33</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8218,7 +8218,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8227,16 +8227,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>67.33</v>
+        <v>66.29</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8250,7 +8250,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8259,16 +8259,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>66.29</v>
+        <v>61.49</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8282,7 +8282,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8291,16 +8291,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>61.49</v>
+        <v>59.51</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8314,7 +8314,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8323,16 +8323,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>59.51</v>
+        <v>54.46</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8343,28 +8343,28 @@
         <v>2021</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>50</v>
+        <v>386</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>51</v>
+        <v>387</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>54.46</v>
+        <v>81.99</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8375,28 +8375,28 @@
         <v>2021</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D184" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="E184" s="2" t="s">
+      <c r="G184" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F184" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>81.99</v>
+        <v>79.31</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8407,28 +8407,28 @@
         <v>2021</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>79.31</v>
+        <v>77.94</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8442,7 +8442,7 @@
         <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>394</v>
@@ -8451,16 +8451,16 @@
         <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>77.94</v>
+        <v>77.72</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8471,10 +8471,10 @@
         <v>2021</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
@@ -8483,16 +8483,16 @@
         <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>77.72</v>
+        <v>77.36</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8506,7 +8506,7 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>398</v>
@@ -8515,16 +8515,16 @@
         <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>77.36</v>
+        <v>77.04</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8538,7 +8538,7 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>400</v>
@@ -8547,16 +8547,16 @@
         <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>77.04</v>
+        <v>76.9</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8570,7 +8570,7 @@
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>402</v>
@@ -8579,16 +8579,16 @@
         <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>76.9</v>
+        <v>76.86</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8599,10 +8599,10 @@
         <v>2021</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>404</v>
@@ -8611,16 +8611,16 @@
         <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>76.86</v>
+        <v>76.46</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8634,7 +8634,7 @@
         <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>406</v>
@@ -8643,16 +8643,16 @@
         <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>76.46</v>
+        <v>76.29</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8663,10 +8663,10 @@
         <v>2021</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>408</v>
@@ -8675,16 +8675,16 @@
         <v>409</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>76.29</v>
+        <v>76.17</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8695,28 +8695,28 @@
         <v>2021</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>410</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>76.17</v>
+        <v>76.09</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8727,28 +8727,28 @@
         <v>2021</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D195" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E195" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="F195" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>76.09</v>
+        <v>75.99</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8759,10 +8759,10 @@
         <v>2021</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>413</v>
@@ -8771,16 +8771,16 @@
         <v>414</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>75.99</v>
+        <v>75.97</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8794,7 +8794,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>415</v>
@@ -8803,16 +8803,16 @@
         <v>416</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>75.97</v>
+        <v>75.81</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8823,28 +8823,28 @@
         <v>2021</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>75.81</v>
+        <v>75.72</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8855,10 +8855,10 @@
         <v>2021</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>420</v>
@@ -8867,16 +8867,16 @@
         <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>75.72</v>
+        <v>75.5</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8887,28 +8887,28 @@
         <v>2021</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>75.5</v>
+        <v>75.49</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8922,7 +8922,7 @@
         <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>425</v>
@@ -8931,16 +8931,16 @@
         <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>75.49</v>
+        <v>74.98</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8951,10 +8951,10 @@
         <v>2021</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
@@ -8963,16 +8963,16 @@
         <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>74.98</v>
+        <v>74.82</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8983,10 +8983,10 @@
         <v>2021</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>429</v>
@@ -8995,16 +8995,16 @@
         <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>74.82</v>
+        <v>74.67</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9015,10 +9015,10 @@
         <v>2021</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
@@ -9027,16 +9027,16 @@
         <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>74.67</v>
+        <v>74.51</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9047,10 +9047,10 @@
         <v>2021</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -9059,16 +9059,16 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>74.51</v>
+        <v>74.35</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9082,7 +9082,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9091,16 +9091,16 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>74.35</v>
+        <v>74.31</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9114,7 +9114,7 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9123,16 +9123,16 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>74.31</v>
+        <v>74.07</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9146,7 +9146,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
@@ -9155,10 +9155,10 @@
         <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9178,7 +9178,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>441</v>
@@ -9187,10 +9187,10 @@
         <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9210,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>443</v>
@@ -9219,10 +9219,10 @@
         <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9242,7 +9242,7 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>445</v>
@@ -9251,10 +9251,10 @@
         <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9274,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>447</v>
@@ -9283,10 +9283,10 @@
         <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9306,19 +9306,19 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>449</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9347,10 +9347,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9370,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9379,10 +9379,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9402,7 +9402,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9411,10 +9411,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9434,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9443,10 +9443,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9466,7 +9466,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9475,10 +9475,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9498,7 +9498,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9507,10 +9507,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9530,7 +9530,7 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9539,10 +9539,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9562,7 +9562,7 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9571,10 +9571,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9594,7 +9594,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9603,10 +9603,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9626,7 +9626,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9635,10 +9635,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9658,7 +9658,7 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
@@ -9667,10 +9667,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -436,18 +436,18 @@
     <t xml:space="preserve">San Esteban</t>
   </si>
   <si>
+    <t xml:space="preserve">13122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
     <t xml:space="preserve">13301</t>
   </si>
   <si>
     <t xml:space="preserve">Colina</t>
   </si>
   <si>
-    <t xml:space="preserve">13122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
     <t xml:space="preserve">7408</t>
   </si>
   <si>
@@ -1657,18 +1657,18 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
+    <t xml:space="preserve">8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
     <t xml:space="preserve">8201</t>
   </si>
   <si>
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
     <t xml:space="preserve">8306</t>
   </si>
   <si>
@@ -2092,7 +2092,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:01</t>
+    <t xml:space="preserve">2026-09-18 11:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11202</t>
@@ -109,9 +109,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -211,7 +208,7 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16109</t>
@@ -226,7 +223,7 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5606</t>
@@ -931,9 +928,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">13504</t>
   </si>
   <si>
@@ -1282,7 +1276,7 @@
     <t xml:space="preserve">Salamanca</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1402</t>
@@ -1447,7 +1441,7 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8103</t>
@@ -1507,7 +1501,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14201</t>
@@ -1519,10 +1513,10 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">Los Álamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9101</t>
@@ -1828,7 +1822,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">8309</t>
@@ -2104,7 +2098,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-10-05 17:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2796,7 +2790,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2825,10 +2819,10 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2857,10 +2851,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2889,10 +2883,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2921,10 +2915,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2953,10 +2947,10 @@
         <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -2985,10 +2979,10 @@
         <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3017,10 +3011,10 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3049,10 +3043,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3078,19 +3072,19 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -3110,19 +3104,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3142,19 +3136,19 @@
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3174,19 +3168,19 @@
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3206,19 +3200,19 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3238,19 +3232,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3270,25 +3264,25 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>78.62</v>
+        <v>78.63</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3302,19 +3296,19 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3334,25 +3328,25 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3366,19 +3360,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3398,19 +3392,19 @@
         <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3430,19 +3424,19 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3462,19 +3456,19 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3494,19 +3488,19 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3526,19 +3520,19 @@
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3558,19 +3552,19 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3590,19 +3584,19 @@
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3622,19 +3616,19 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3654,19 +3648,19 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3686,19 +3680,19 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3718,19 +3712,19 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3750,19 +3744,19 @@
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3782,19 +3776,19 @@
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3814,19 +3808,19 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3846,19 +3840,19 @@
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3878,19 +3872,19 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3910,19 +3904,19 @@
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3942,19 +3936,19 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -3974,19 +3968,19 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4006,19 +4000,19 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4038,19 +4032,19 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4070,19 +4064,19 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4102,19 +4096,19 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4134,19 +4128,19 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4166,19 +4160,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4198,19 +4192,19 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4230,19 +4224,19 @@
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4262,19 +4256,19 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4294,19 +4288,19 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4326,19 +4320,19 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4358,19 +4352,19 @@
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4390,19 +4384,19 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4422,19 +4416,19 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4454,19 +4448,19 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4486,19 +4480,19 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4518,19 +4512,19 @@
         <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4550,19 +4544,19 @@
         <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4582,19 +4576,19 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4614,19 +4608,19 @@
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4646,19 +4640,19 @@
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4678,19 +4672,19 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4710,19 +4704,19 @@
         <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4742,19 +4736,19 @@
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4774,19 +4768,19 @@
         <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4806,19 +4800,19 @@
         <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4838,19 +4832,19 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4870,19 +4864,19 @@
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4902,19 +4896,19 @@
         <v>13</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4934,19 +4928,19 @@
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4966,19 +4960,19 @@
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -4998,19 +4992,19 @@
         <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5030,19 +5024,19 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5062,19 +5056,19 @@
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5094,19 +5088,19 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5126,19 +5120,19 @@
         <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5158,19 +5152,19 @@
         <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5190,19 +5184,19 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5222,19 +5216,19 @@
         <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5254,19 +5248,19 @@
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5286,19 +5280,19 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5318,19 +5312,19 @@
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5350,19 +5344,19 @@
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5382,19 +5376,19 @@
         <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5414,19 +5408,19 @@
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5446,19 +5440,19 @@
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5478,19 +5472,19 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5510,19 +5504,19 @@
         <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5542,19 +5536,19 @@
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5574,19 +5568,19 @@
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5606,19 +5600,19 @@
         <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5638,19 +5632,19 @@
         <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5670,19 +5664,19 @@
         <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5702,19 +5696,19 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5734,19 +5728,19 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5766,19 +5760,19 @@
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5798,19 +5792,19 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5830,19 +5824,19 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5862,19 +5856,19 @@
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5894,19 +5888,19 @@
         <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5926,19 +5920,19 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D107" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5958,19 +5952,19 @@
         <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -5990,19 +5984,19 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6022,19 +6016,19 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6054,19 +6048,19 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6086,19 +6080,19 @@
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6118,19 +6112,19 @@
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6150,19 +6144,19 @@
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6182,19 +6176,19 @@
         <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6214,19 +6208,19 @@
         <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6246,19 +6240,19 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6278,19 +6272,19 @@
         <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6310,19 +6304,19 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6342,19 +6336,19 @@
         <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6374,19 +6368,19 @@
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6406,19 +6400,19 @@
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6438,19 +6432,19 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6470,19 +6464,19 @@
         <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D124" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6502,19 +6496,19 @@
         <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6534,19 +6528,19 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D126" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6566,19 +6560,19 @@
         <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6598,19 +6592,19 @@
         <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D128" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6630,19 +6624,19 @@
         <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D129" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6662,19 +6656,19 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D130" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6694,19 +6688,19 @@
         <v>6</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D131" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6726,19 +6720,19 @@
         <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6758,19 +6752,19 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D133" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6790,19 +6784,19 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D134" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6822,19 +6816,19 @@
         <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D135" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6854,19 +6848,19 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D136" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6886,19 +6880,19 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6918,19 +6912,19 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6950,19 +6944,19 @@
         <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -6982,19 +6976,19 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D140" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7014,19 +7008,19 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D141" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7046,19 +7040,19 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D142" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E142" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7078,19 +7072,19 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>304</v>
+        <v>68</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7110,19 +7104,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7142,19 +7136,19 @@
         <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7174,19 +7168,19 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7206,19 +7200,19 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7238,19 +7232,19 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7270,19 +7264,19 @@
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7302,19 +7296,19 @@
         <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7334,19 +7328,19 @@
         <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7366,19 +7360,19 @@
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7398,19 +7392,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7430,19 +7424,19 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7462,19 +7456,19 @@
         <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7494,19 +7488,19 @@
         <v>6</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7526,19 +7520,19 @@
         <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7558,19 +7552,19 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7590,19 +7584,19 @@
         <v>16</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7622,19 +7616,19 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7654,19 +7648,19 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7686,19 +7680,19 @@
         <v>6</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7718,19 +7712,19 @@
         <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7750,19 +7744,19 @@
         <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7782,19 +7776,19 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7814,19 +7808,19 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7846,19 +7840,19 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7878,19 +7872,19 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7910,19 +7904,19 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7942,19 +7936,19 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7974,19 +7968,19 @@
         <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8006,19 +8000,19 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8038,19 +8032,19 @@
         <v>5</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8070,19 +8064,19 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8102,19 +8096,19 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8134,19 +8128,19 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8166,19 +8160,19 @@
         <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8198,19 +8192,19 @@
         <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8230,19 +8224,19 @@
         <v>6</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8262,19 +8256,19 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8294,19 +8288,19 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8326,19 +8320,19 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8358,19 +8352,19 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8390,19 +8384,19 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8422,19 +8416,19 @@
         <v>15</v>
       </c>
       <c r="C185" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="F185" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="E185" s="2" t="s">
+      <c r="G185" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8454,19 +8448,19 @@
         <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D186" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="F186" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8486,19 +8480,19 @@
         <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D187" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="F187" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8518,19 +8512,19 @@
         <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8550,19 +8544,19 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8582,19 +8576,19 @@
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8614,19 +8608,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8646,19 +8640,19 @@
         <v>3</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8678,19 +8672,19 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8710,19 +8704,19 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8742,19 +8736,19 @@
         <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8774,19 +8768,19 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8806,19 +8800,19 @@
         <v>15</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8838,19 +8832,19 @@
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8870,19 +8864,19 @@
         <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8902,19 +8896,19 @@
         <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="F200" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8934,19 +8928,19 @@
         <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8966,19 +8960,19 @@
         <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="F202" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -8998,19 +8992,19 @@
         <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9030,19 +9024,19 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9062,19 +9056,19 @@
         <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9094,19 +9088,19 @@
         <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9126,19 +9120,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9158,19 +9152,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9190,19 +9184,19 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9222,19 +9216,19 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9254,19 +9248,19 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9286,19 +9280,19 @@
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9318,19 +9312,19 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9350,19 +9344,19 @@
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9382,19 +9376,19 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9414,19 +9408,19 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9446,19 +9440,19 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9478,19 +9472,19 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9510,19 +9504,19 @@
         <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9542,19 +9536,19 @@
         <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9574,19 +9568,19 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9606,19 +9600,19 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9638,19 +9632,19 @@
         <v>2</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9670,19 +9664,19 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9702,19 +9696,19 @@
         <v>1</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9734,19 +9728,19 @@
         <v>2</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9766,19 +9760,19 @@
         <v>8</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="F227" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E227" s="2" t="s">
+      <c r="G227" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9798,19 +9792,19 @@
         <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9830,19 +9824,19 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9862,19 +9856,19 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9894,19 +9888,19 @@
         <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9926,19 +9920,19 @@
         <v>8</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9958,19 +9952,19 @@
         <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="F233" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9990,19 +9984,19 @@
         <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10022,19 +10016,19 @@
         <v>14</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="F235" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10054,19 +10048,19 @@
         <v>8</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10086,19 +10080,19 @@
         <v>9</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10118,19 +10112,19 @@
         <v>9</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10150,19 +10144,19 @@
         <v>9</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10182,19 +10176,19 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10214,19 +10208,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10246,19 +10240,19 @@
         <v>9</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10278,19 +10272,19 @@
         <v>14</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10310,19 +10304,19 @@
         <v>14</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10342,19 +10336,19 @@
         <v>9</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10374,19 +10368,19 @@
         <v>9</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10406,19 +10400,19 @@
         <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10438,19 +10432,19 @@
         <v>14</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10470,19 +10464,19 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10502,19 +10496,19 @@
         <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10534,19 +10528,19 @@
         <v>14</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10566,19 +10560,19 @@
         <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10598,19 +10592,19 @@
         <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10630,19 +10624,19 @@
         <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10662,19 +10656,19 @@
         <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10694,19 +10688,19 @@
         <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10726,19 +10720,19 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10758,19 +10752,19 @@
         <v>14</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10790,19 +10784,19 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10822,19 +10816,19 @@
         <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10854,19 +10848,19 @@
         <v>8</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10886,19 +10880,19 @@
         <v>8</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10918,19 +10912,19 @@
         <v>8</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10950,19 +10944,19 @@
         <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10982,19 +10976,19 @@
         <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11014,19 +11008,19 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11046,19 +11040,19 @@
         <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11078,19 +11072,19 @@
         <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11110,19 +11104,19 @@
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11142,19 +11136,19 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11174,19 +11168,19 @@
         <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11206,19 +11200,19 @@
         <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11238,19 +11232,19 @@
         <v>10</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11270,19 +11264,19 @@
         <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11302,19 +11296,19 @@
         <v>8</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11334,19 +11328,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11366,19 +11360,19 @@
         <v>9</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11398,19 +11392,19 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11430,19 +11424,19 @@
         <v>8</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11462,19 +11456,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11494,19 +11488,19 @@
         <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11526,19 +11520,19 @@
         <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11558,19 +11552,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11590,19 +11584,19 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11622,19 +11616,19 @@
         <v>8</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11654,19 +11648,19 @@
         <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11686,19 +11680,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11718,19 +11712,19 @@
         <v>8</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11750,19 +11744,19 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11782,19 +11776,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11814,19 +11808,19 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11846,19 +11840,19 @@
         <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11878,19 +11872,19 @@
         <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11910,19 +11904,19 @@
         <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11942,19 +11936,19 @@
         <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11974,19 +11968,19 @@
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12006,19 +12000,19 @@
         <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12038,19 +12032,19 @@
         <v>14</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12070,19 +12064,19 @@
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12102,19 +12096,19 @@
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12134,19 +12128,19 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12166,19 +12160,19 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12198,19 +12192,19 @@
         <v>8</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12230,19 +12224,19 @@
         <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12262,19 +12256,19 @@
         <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12294,19 +12288,19 @@
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12326,19 +12320,19 @@
         <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12358,19 +12352,19 @@
         <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12390,19 +12384,19 @@
         <v>9</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12422,19 +12416,19 @@
         <v>14</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12454,19 +12448,19 @@
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12486,19 +12480,19 @@
         <v>14</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12518,19 +12512,19 @@
         <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12550,19 +12544,19 @@
         <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12582,19 +12576,19 @@
         <v>10</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12614,19 +12608,19 @@
         <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12646,19 +12640,19 @@
         <v>8</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12678,19 +12672,19 @@
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12710,19 +12704,19 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12742,19 +12736,19 @@
         <v>8</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12774,19 +12768,19 @@
         <v>14</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12806,19 +12800,19 @@
         <v>10</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12838,19 +12832,19 @@
         <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12870,19 +12864,19 @@
         <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12902,19 +12896,19 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12934,19 +12928,19 @@
         <v>10</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -12966,19 +12960,19 @@
         <v>10</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -12998,19 +12992,19 @@
         <v>10</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13030,19 +13024,19 @@
         <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13062,19 +13056,19 @@
         <v>9</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13094,19 +13088,19 @@
         <v>9</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13126,19 +13120,19 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13168,7 +13162,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13176,50 +13170,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -13241,21 +13235,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13264,7 +13258,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
